--- a/fund.xlsx
+++ b/fund.xlsx
@@ -901,66 +901,66 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>008777</t>
+          <t>110020</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>华安沪深300ETF联接C</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>40.16</t>
+          <t>易方达沪深300ETF联接A</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>4332.99</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04999999999999982</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.03000000000000025</v>
+        <v>0.2400000000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1299999999999999</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2100000000000009</v>
+        <v>-0.25</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6500000000000021</v>
+        <v>-1.290000000000003</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1</v>
+        <v>-0.9499999999999993</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5599999999999987</v>
+        <v>0.6100000000000012</v>
       </c>
       <c r="K8" t="n">
-        <v>1.209999999999999</v>
+        <v>0.8899999999999988</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9900000000000002</v>
+        <v>-1.24</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>3.15</v>
+        <v>3.420000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.66</v>
+        <v>-1.47</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-10.79</v>
+        <v>-10.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7.469999999999999</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>1.299999999999999</v>
+        <v>1.449999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>2.57</v>
+        <v>3.74</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-22.09</v>
+        <v>-22.41</v>
       </c>
     </row>
     <row r="9">
@@ -1789,16 +1789,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>515580</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>消费ETF汇添富</t>
+          <t>科技100ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.998</v>
+        <v>2.5925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>45.71</v>
+        <v>54.4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1833,37 +1833,37 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>37.83</v>
+        <v>118.48</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4615</v>
+        <v>0.8244</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>14.5</v>
+        <v>15.3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0.823</v>
+        <v>1.302</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1886,14 +1886,14 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>53.1</v>
+        <v>38.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -1904,16 +1904,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.3939</v>
+        <v>1.5867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>52.5</v>
+        <v>54.28</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>115.28</v>
+        <v>111.06</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1967,18 +1967,18 @@
         <v>-1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7738</v>
+        <v>0.8437</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>14.2</v>
+        <v>15.7</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.733</v>
+        <v>1.328</v>
       </c>
       <c r="W3" t="n">
-        <v>95.3</v>
+        <v>86.7</v>
       </c>
       <c r="X3" t="n">
         <v>-1</v>
@@ -2001,14 +2001,14 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>24.8</v>
+        <v>38.31</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2019,16 +2019,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>012805</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7988</v>
+        <v>5.1573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>50.97</v>
+        <v>61.84</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>105.68</v>
+        <v>109.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2082,18 +2082,18 @@
         <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7356</v>
+        <v>0.9463</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -2101,29 +2101,29 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>1.464</v>
+        <v>0.707</v>
       </c>
       <c r="W4" t="n">
-        <v>62.1</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
       <c r="AA4" t="n">
-        <v>53.89</v>
+        <v>18.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -2134,16 +2134,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.4133</v>
+        <v>1.7742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2159,15 +2159,15 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>60.57</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>119.81</v>
+        <v>101.26</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>-1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9698</v>
+        <v>0.9928</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2205,21 +2205,21 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="T5" t="n">
-        <v>15.1</v>
+        <v>49.5</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.877</v>
+        <v>0.04</v>
       </c>
       <c r="W5" t="n">
-        <v>95.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="X5" t="n">
         <v>-1</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>38.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2.5</v>
+        <v>-3</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2249,16 +2249,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.3163</v>
+        <v>1.5464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>66.23</v>
+        <v>60.13</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>112.3</v>
+        <v>110.86</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.0512</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>-1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>18.9</v>
+        <v>15.9</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.025</v>
+        <v>0.092</v>
       </c>
       <c r="W6" t="n">
-        <v>95.7</v>
+        <v>99.2</v>
       </c>
       <c r="X6" t="n">
         <v>-1</v>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>31.24</v>
+        <v>3.91</v>
       </c>
       <c r="AB6" t="n">
         <v>-2.5</v>
@@ -2364,16 +2364,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>110020</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>易方达沪深300ETF联接A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.5977</v>
+        <v>1.8842</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>56.28</v>
+        <v>58.41</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>117.34</v>
+        <v>114.82</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>-1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9045</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>-1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>16</v>
+        <v>14.9</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2446,17 +2446,17 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.289</v>
+        <v>0.898</v>
       </c>
       <c r="W7" t="n">
-        <v>97.3</v>
+        <v>79.8</v>
       </c>
       <c r="X7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>38.31</v>
+        <v>37.1</v>
       </c>
       <c r="AB7" t="n">
         <v>-2.5</v>
@@ -2479,16 +2479,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>515580</t>
+          <t>008115</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>科技100ETF华泰柏瑞</t>
+          <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.6115</v>
+        <v>1.7659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>56.35</v>
+        <v>47.29</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2523,37 +2523,37 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>121.41</v>
+        <v>24.57</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8925</v>
+        <v>0.4002</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>15.6</v>
+        <v>12.1</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.304</v>
+        <v>0.525</v>
       </c>
       <c r="W8" t="n">
-        <v>97.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="X8" t="n">
         <v>-1</v>
@@ -2576,14 +2576,14 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>38.9</v>
+        <v>13.26</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -2594,20 +2594,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>007029</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>易方达中证500ETF联接发起式C</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.7093</v>
+        <v>1.8901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>57.04</v>
+        <v>54.25</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>19.89</v>
+        <v>110.75</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2650,55 +2650,55 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5132</v>
+        <v>0.8414</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>33.7</v>
+        <v>15.8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>2.73</v>
+        <v>1.264</v>
       </c>
       <c r="W9" t="n">
-        <v>99.3</v>
+        <v>86.7</v>
       </c>
       <c r="X9" t="n">
         <v>-1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
       <c r="AA9" t="n">
-        <v>31.68</v>
+        <v>36.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2709,16 +2709,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>012832</t>
+          <t>000216</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>南方中证新能源ETF联接C</t>
+          <t>华安黄金ETF联接A</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.7315</v>
+        <v>3.6598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>55.18</v>
+        <v>50.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2753,26 +2753,26 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>114.92</v>
+        <v>77.36</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7138</v>
+        <v>0.6774</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2791,29 +2791,29 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1.566</v>
+        <v>1.685</v>
       </c>
       <c r="W10" t="n">
-        <v>67</v>
+        <v>79.3</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
       <c r="AA10" t="n">
-        <v>65.01000000000001</v>
+        <v>25.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -2824,16 +2824,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>消费ETF汇添富</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.4419</v>
+        <v>3.0091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>53.92</v>
+        <v>47.31</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2868,37 +2868,37 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>116.38</v>
+        <v>54.18</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8133</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2906,13 +2906,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.386</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>96.8</v>
+        <v>11.1</v>
       </c>
       <c r="X11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>12.06</v>
+        <v>53.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>-2.5</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -2939,16 +2939,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.7738</v>
+        <v>2.3906</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2964,15 +2964,15 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>85.16</v>
+        <v>51.85</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>101.26</v>
+        <v>115.28</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3002,48 +3002,48 @@
         <v>-1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.968</v>
+        <v>0.7489</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>49.4</v>
+        <v>14.1</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.038</v>
+        <v>0.725</v>
       </c>
       <c r="W12" t="n">
-        <v>99.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="X12" t="n">
         <v>-1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>1.88</v>
+        <v>24.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3054,16 +3054,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>008777</t>
+          <t>012832</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华安沪深300ETF联接C</t>
+          <t>南方中证新能源ETF联接C</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.134</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>60.35</v>
+        <v>54.11</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>119.92</v>
+        <v>111.32</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3117,18 +3117,18 @@
         <v>-1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9645</v>
+        <v>0.6775</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>15.3</v>
+        <v>12.8</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3136,29 +3136,29 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.923</v>
+        <v>1.605</v>
       </c>
       <c r="W13" t="n">
-        <v>93.09999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="AB13" t="n">
         <v>-1</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="AA13" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>-2.5</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3169,16 +3169,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>007029</t>
+          <t>012805</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>易方达中证500ETF联接发起式C</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.9035</v>
+        <v>0.7941</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>56.39</v>
+        <v>49.52</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>117.33</v>
+        <v>100.12</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3232,18 +3232,18 @@
         <v>-1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9064</v>
+        <v>0.6754</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>16.1</v>
+        <v>20.4</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3251,29 +3251,29 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1.227</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
-        <v>97.3</v>
+        <v>48.1</v>
       </c>
       <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="AB14" t="n">
         <v>-1</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="AA14" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>-2.5</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3284,16 +3284,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>011555</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>海富通欣利混合C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.1573</v>
+        <v>1.4391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>61.84</v>
+        <v>52.11</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>109.8</v>
+        <v>111.04</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3347,18 +3347,18 @@
         <v>-1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9463</v>
+        <v>0.749</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>20.2</v>
+        <v>14.8</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3366,29 +3366,29 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.707</v>
+        <v>0.389</v>
       </c>
       <c r="W15" t="n">
-        <v>94.2</v>
+        <v>93.7</v>
       </c>
       <c r="X15" t="n">
         <v>-1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
       <c r="AA15" t="n">
-        <v>18.73</v>
+        <v>12.06</v>
       </c>
       <c r="AB15" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3399,16 +3399,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>008115</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>天弘中证红利低波动100联接C</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.7621</v>
+        <v>2.401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>45.7</v>
+        <v>58.38</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>16.24</v>
+        <v>114.77</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3455,25 +3455,25 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3489</v>
+        <v>0.9116</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T16" t="n">
-        <v>12.4</v>
+        <v>14.8</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -3481,29 +3481,29 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.511</v>
+        <v>0.894</v>
       </c>
       <c r="W16" t="n">
-        <v>94.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>13.26</v>
+        <v>38.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -3514,16 +3514,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.5472</v>
+        <v>7.3163</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>62.01</v>
+        <v>66.23</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>113.7</v>
+        <v>112.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>-1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.9573</v>
+        <v>1.0512</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>-1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>16.1</v>
+        <v>18.9</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.093</v>
+        <v>1.025</v>
       </c>
       <c r="W17" t="n">
-        <v>99.7</v>
+        <v>93.7</v>
       </c>
       <c r="X17" t="n">
         <v>-1</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>3.91</v>
+        <v>31.24</v>
       </c>
       <c r="AB17" t="n">
         <v>-2.5</v>
@@ -3629,20 +3629,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.6697</v>
+        <v>1.7093</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3654,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>50.66</v>
+        <v>57.04</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3673,15 +3673,15 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>84.42</v>
+        <v>19.89</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6953</v>
+        <v>0.5132</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3703,25 +3703,25 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>12.6</v>
+        <v>33.7</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>1.699</v>
+        <v>2.73</v>
       </c>
       <c r="W18" t="n">
-        <v>97.5</v>
+        <v>94</v>
       </c>
       <c r="X18" t="n">
         <v>-1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>25.07</v>
+        <v>31.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>

--- a/fund.xlsx
+++ b/fund.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -585,53 +585,53 @@
           <t>58.75</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>-3.28</v>
+      <c r="D3" t="n">
+        <v>-1.44</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3600000000000003</v>
+        <v>-1.53</v>
       </c>
       <c r="F3" t="n">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5200000000000005</v>
+        <v>-0.75</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.420000000000002</v>
+        <v>-6.440000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.67</v>
+        <v>-0.6500000000000004</v>
       </c>
       <c r="J3" t="n">
-        <v>17.52</v>
+        <v>17.59</v>
       </c>
       <c r="K3" t="n">
-        <v>18.04</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>-4.220000000000001</v>
+        <v>17.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.73</v>
       </c>
       <c r="N3" t="n">
-        <v>2.82</v>
+        <v>0.4199999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.21</v>
+        <v>-0.07999999999999999</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-11.1</v>
+        <v>-11.02</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-12.24</v>
+        <v>-13.87</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7299999999999986</v>
+        <v>1.220000000000001</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>20.65</v>
+        <v>21.57</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.26</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="4">
@@ -651,52 +651,52 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-6.05</v>
+        <v>-2.35</v>
       </c>
       <c r="E4" t="n">
-        <v>1.73</v>
+        <v>-0.7899999999999998</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>5.850000000000001</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>-6.31</v>
+        <v>6.220000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-5.29</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-15.13</v>
+        <v>-17.31</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.85</v>
+        <v>-4.23</v>
       </c>
       <c r="J4" t="n">
-        <v>19.77</v>
+        <v>19.13</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>41.36</v>
+        <v>39.11</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>-6.99</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>4.91</v>
+        <v>-1.64</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.16</v>
       </c>
       <c r="O4" t="n">
-        <v>4.32</v>
+        <v>4.45</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-16.89</v>
+        <v>-15.56</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-21.95</v>
+        <v>-24.73999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.450000000000001</v>
+        <v>-2.359999999999999</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>22.9</v>
+        <v>23.11</v>
       </c>
       <c r="T4" t="n">
-        <v>18.06</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="5">
@@ -716,52 +716,52 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-5.17</v>
+        <v>-2.53</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3099999999999996</v>
+        <v>-1.63</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1199999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-11.33</v>
+        <v>-10.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-21.13</v>
+        <v>-22.76</v>
       </c>
       <c r="I5" t="n">
         <v>-11.07</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.509999999999998</v>
+        <v>-4.27</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.030000000000001</v>
+        <v>-5.06</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-6.11</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>3.49</v>
+        <v>-1.82</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3199999999999998</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.65</v>
+        <v>-1.32</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-21.91</v>
+        <v>-20.97</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-27.95</v>
+        <v>-30.19</v>
       </c>
       <c r="R5" t="n">
-        <v>-8.67</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.379999999999999</v>
+        <v>-0.2899999999999991</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-27.33</v>
+        <v>-27.88</v>
       </c>
     </row>
     <row r="6">
@@ -780,53 +780,53 @@
           <t>40.62</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>2.149999999999999</v>
+      <c r="D6" t="n">
+        <v>0.9099999999999999</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-4.55</v>
+        <v>-3.569999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1</v>
+        <v>-1.38</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>10.96</v>
+        <v>9.84</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>25.97</v>
+        <v>29.44</v>
       </c>
       <c r="I6" t="n">
-        <v>2.260000000000002</v>
+        <v>1.459999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.649999999999999</v>
+        <v>-6.949999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>23.31</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.209999999999999</v>
+        <v>23.03</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>1.62</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.369999999999999</v>
+        <v>-1.62</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.63</v>
+        <v>-3.15</v>
       </c>
       <c r="P6" t="n">
-        <v>0.379999999999999</v>
+        <v>-0.4299999999999997</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>19.15</v>
+        <v>22.01000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>4.66</v>
+        <v>3.33</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.52</v>
+        <v>-2.969999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.009999999999999787</v>
+        <v>0.2099999999999991</v>
       </c>
     </row>
     <row r="7">
@@ -846,25 +846,25 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4.13</v>
+        <v>2.470000000000001</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-6.02</v>
+        <v>-6.1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="G7" t="n">
-        <v>4.629999999999999</v>
+        <v>5.17</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>29.13</v>
+        <v>29.92</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-21.99</v>
+        <v>-20.9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-21.59</v>
+        <v>-22.52</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -872,25 +872,25 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-2.84</v>
+        <v>3.180000000000001</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-4.15</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>7.17</v>
+        <v>6.05</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.950000000000001</v>
+        <v>-5.1</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>22.31</v>
+        <v>22.49</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-19.59</v>
+        <v>-19.03</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-18.46</v>
+        <v>-18.54</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -915,52 +915,52 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.2999999999999998</v>
+        <v>-0.09999999999999987</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2400000000000002</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.07000000000000006</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.25</v>
+        <v>-0.1800000000000002</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.290000000000003</v>
+        <v>-1.41</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9499999999999993</v>
+        <v>-0.8000000000000007</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6100000000000012</v>
+        <v>0.5299999999999994</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8899999999999988</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>3.420000000000001</v>
+        <v>0.6100000000000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.47</v>
+        <v>-1.7</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-10.83</v>
+        <v>-10.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>-8.109999999999999</v>
+        <v>-8.839999999999996</v>
       </c>
       <c r="R8" t="n">
-        <v>1.449999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="S8" t="n">
-        <v>3.74</v>
+        <v>4.51</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-22.41</v>
+        <v>-21.99</v>
       </c>
     </row>
     <row r="9">
@@ -980,645 +980,710 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6299999999999999</v>
+        <v>-0.77</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.81</v>
+        <v>-1.75</v>
       </c>
       <c r="F9" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.469999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>4.989999999999998</v>
+        <v>5.48</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.489999999999999</v>
+        <v>-2.860000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.76</v>
+        <v>-3.67</v>
       </c>
       <c r="K9" t="n">
-        <v>23.05</v>
+        <v>22.54</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3100000000000005</v>
+        <v>-0.06000000000000005</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3700000000000001</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.05</v>
+        <v>-0.04999999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8800000000000008</v>
+        <v>-0.8000000000000007</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.829999999999998</v>
+        <v>-1.949999999999996</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.090000000000001</v>
+        <v>-0.9900000000000002</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3699999999999992</v>
+        <v>0.3100000000000005</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.25</v>
+        <v>-0.2799999999999994</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>040046</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>110026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>易方达创业板ETF联接A</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>418.53</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.7400000000000002</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>-5.36</v>
+          <t>2521.21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.56</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.720000000000001</v>
-      </c>
-      <c r="H10" t="n">
-        <v>5.759999999999998</v>
+        <v>6.789999999999999</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>32.15000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-9.639999999999999</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>53.04000000000001</v>
+        <v>0.04999999999999893</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>-15.39</v>
       </c>
       <c r="K10" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>-1.680000000000001</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>6.540000000000001</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-6.890000000000001</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>-13.3</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-1.059999999999999</v>
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>24.72000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>-7.24</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>56.17</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-13.05</v>
+        <v>1.92</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-11.41</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-22.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>619.61</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>-1.89</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>-4.51</v>
+          <t>418.53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>4.390000000000001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-4.19</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.680000000000001</v>
+        <v>-1.79</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.07</v>
+        <v>2.439999999999998</v>
       </c>
       <c r="I11" t="n">
-        <v>-5.709999999999999</v>
+        <v>-6.840000000000001</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>37.92</v>
+        <v>51.64</v>
       </c>
       <c r="K11" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>7.33</v>
+        <v>10.05</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.52</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-6.04</v>
+        <v>-5.96</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-12.26</v>
+        <v>-12.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.889999999999997</v>
+        <v>-4.989999999999998</v>
       </c>
       <c r="R11" t="n">
-        <v>-3.31</v>
+        <v>-4.97</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>41.05</v>
+        <v>55.62</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.34</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>012805</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>050025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>655.24</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>-2.47</v>
+          <t>619.61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2.69</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-15.37</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>-7.07</v>
+        <v>1.23</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.7200000000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.860000000000001</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>32.74</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>-3.41</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.920000000000001</v>
+        <v>-4.960000000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-2.630000000000001</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="K12" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>3.18</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>-16.9</v>
+        <v>-5.62</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-17.65</v>
+        <v>-10.99</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>-15.68</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>35.14</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.789999999999999</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
+        <v>-12.39</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.7599999999999998</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-5.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>012805</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>1947.62</t>
+          <t>655.24</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5.209999999999999</v>
+        <v>-2.33</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.09000000000000008</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-9.290000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1500000000000021</v>
+        <v>-7.129999999999999</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20.76000000000001</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>37.63</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>34.5</v>
+        <v>35.32</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-4.9</v>
+        <v>-1.62</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-5.370000000000001</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-6.969999999999999</v>
+        <v>2.04</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>-15.87</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>-19.56</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-14.56</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>23.16</v>
-      </c>
-      <c r="S13" s="2" t="n">
-        <v>40.76</v>
-      </c>
-      <c r="T13" t="n">
-        <v>11.2</v>
+        <v>37.19</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.08000000000000007</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>000216</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>华安黄金ETF联接A</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1947.62</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2399999999999984</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>24.91</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>32.62</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>9.069999999999999</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-7.189999999999998</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="T14" t="n">
+        <v>9.799999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>006476</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>南方原油C</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>271.58</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>-9.01</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>9.899999999999999</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-4.56</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>-19.49</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>-30.78</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>25.99</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>78.06999999999999</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>49.51000000000001</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>-15.14</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>-26.31</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>-28.38</v>
-      </c>
-      <c r="S14" s="2" t="n">
-        <v>29.12</v>
-      </c>
-      <c r="T14" s="2" t="n">
-        <v>54.77</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>交银优选回报灵活配置混合C</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="D15" s="3" t="n">
+        <v>-9.98</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-25.06</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>-27.62</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>-9.27</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>-32.48999999999999</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>-25.75</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>47.4</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>名字</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>基金经理管理规模</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>近一周</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1周~1月</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1月~3月</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>3月~6月</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>6月~1年</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1年~2年</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2年~3年</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>3年~5年</t>
-        </is>
-      </c>
+          <t>易方达中债新综指发起式(LOF)A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>近一周</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>1周~1月</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>1月~3月</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>3月~6月</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>6月~1年</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1年~2年</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>2年~3年</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>3年~5年</t>
-        </is>
-      </c>
+          <t>交银优选回报灵活配置混合C</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>代码</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>111.88</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-3.19</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>-7.48</v>
+          <t>基金经理管理规模</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>近一周</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1周~1月</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1月~3月</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3月~6月</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6月~1年</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1年~2年</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2年~3年</t>
+        </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Q20" s="2" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.2</v>
+          <t>3年~5年</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>近一周</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1周~1月</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1月~3月</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>3月~6月</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6月~1年</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1年~2年</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2年~3年</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
+          <t>3年~5年</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>011555</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>海富通欣利混合C</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>111.88</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>8.739999999999998</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>-7.22</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>161119</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>842.65</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>0.8400000000000001</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-0.02999999999999992</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-2.92</v>
-      </c>
-      <c r="R21" s="2" t="n">
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0.04000000000000001</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.9</v>
-      </c>
-      <c r="S21" s="2" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.999999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1632,7 +1697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -1789,20 +1854,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>515580</t>
+          <t>012832</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技100ETF华泰柏瑞</t>
+          <t>南方中证新能源ETF联接C</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.5925</v>
+        <v>0.7462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1814,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>54.4</v>
+        <v>59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1833,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>118.48</v>
+        <v>118.33</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1852,7 +1917,7 @@
         <v>-1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8244</v>
+        <v>0.8681</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -1863,7 +1928,7 @@
         <v>-1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1871,17 +1936,17 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>1.302</v>
+        <v>1.613</v>
       </c>
       <c r="W2" t="n">
-        <v>88.90000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="X2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1890,7 +1955,7 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>38.9</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AB2" t="n">
         <v>-2.5</v>
@@ -1904,20 +1969,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.5867</v>
+        <v>5.2477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1929,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>54.28</v>
+        <v>67.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1948,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>111.06</v>
+        <v>105.56</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1967,7 +2032,7 @@
         <v>-1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8437</v>
+        <v>0.9643</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1978,7 +2043,7 @@
         <v>-1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>15.7</v>
+        <v>22.8</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1986,17 +2051,17 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>1.328</v>
+        <v>0.71</v>
       </c>
       <c r="W3" t="n">
-        <v>86.7</v>
+        <v>98</v>
       </c>
       <c r="X3" t="n">
         <v>-1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -2005,7 +2070,7 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>38.31</v>
+        <v>18.73</v>
       </c>
       <c r="AB3" t="n">
         <v>-2.5</v>
@@ -2019,20 +2084,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>007029</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>易方达中证500ETF联接发起式C</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.1573</v>
+        <v>1.9222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2044,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>61.84</v>
+        <v>58.58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2063,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>109.8</v>
+        <v>111.92</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2082,7 +2147,7 @@
         <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9463</v>
+        <v>0.9996</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2093,7 +2158,7 @@
         <v>-1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>20.2</v>
+        <v>15.9</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -2101,10 +2166,10 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.707</v>
+        <v>1.264</v>
       </c>
       <c r="W4" t="n">
-        <v>95.40000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="X4" t="n">
         <v>-1</v>
@@ -2116,11 +2181,11 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>18.73</v>
+        <v>36.5</v>
       </c>
       <c r="AB4" t="n">
         <v>-2.5</v>
@@ -2143,11 +2208,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.7742</v>
+        <v>1.7737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2159,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>85.76000000000001</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2178,26 +2243,26 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>101.26</v>
+        <v>98.12</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9928</v>
+        <v>0.904</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2208,7 +2273,7 @@
         <v>-1</v>
       </c>
       <c r="T5" t="n">
-        <v>49.5</v>
+        <v>50.6</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2216,10 +2281,10 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="W5" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="X5" t="n">
         <v>-1</v>
@@ -2249,20 +2314,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>110026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>易方达创业板ETF联接A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.5464</v>
+        <v>3.6826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2274,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>60.13</v>
+        <v>67.64</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2293,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>110.86</v>
+        <v>114.69</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2312,7 +2377,7 @@
         <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9068000000000001</v>
+        <v>1.0708</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2323,7 +2388,7 @@
         <v>-1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>15.9</v>
+        <v>15.4</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2331,10 +2396,10 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.092</v>
+        <v>1.602</v>
       </c>
       <c r="W6" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="X6" t="n">
         <v>-1</v>
@@ -2350,7 +2415,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>3.91</v>
+        <v>54.99</v>
       </c>
       <c r="AB6" t="n">
         <v>-2.5</v>
@@ -2364,20 +2429,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>110020</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>易方达沪深300ETF联接A</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.8842</v>
+        <v>2.3998</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2389,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>58.41</v>
+        <v>53.75</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2408,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>114.82</v>
+        <v>115.84</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2427,7 +2492,7 @@
         <v>-1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.8985</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2438,7 +2503,7 @@
         <v>-1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>14.9</v>
+        <v>13.6</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2446,26 +2511,26 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.898</v>
+        <v>0.698</v>
       </c>
       <c r="W7" t="n">
-        <v>79.8</v>
+        <v>93.5</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>37.1</v>
+        <v>24.8</v>
       </c>
       <c r="AB7" t="n">
         <v>-2.5</v>
@@ -2488,11 +2553,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.7659</v>
+        <v>1.7653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2504,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>47.29</v>
+        <v>47.05</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2523,15 +2588,15 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>24.57</v>
+        <v>60.18</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -2542,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4002</v>
+        <v>0.4129</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2553,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -2561,10 +2626,10 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.525</v>
+        <v>0.486</v>
       </c>
       <c r="W8" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>-1</v>
@@ -2583,7 +2648,7 @@
         <v>13.26</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -2594,20 +2659,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>007029</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>易方达中证500ETF联接发起式C</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.8901</v>
+        <v>1.6144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2619,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>54.25</v>
+        <v>58.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2638,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>110.75</v>
+        <v>111.89</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2657,7 +2722,7 @@
         <v>-1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8414</v>
+        <v>1</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2676,17 +2741,17 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1.264</v>
+        <v>1.329</v>
       </c>
       <c r="W9" t="n">
-        <v>86.7</v>
+        <v>89.8</v>
       </c>
       <c r="X9" t="n">
         <v>-1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2695,7 +2760,7 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>36.5</v>
+        <v>38.31</v>
       </c>
       <c r="AB9" t="n">
         <v>-2.5</v>
@@ -2718,11 +2783,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.6598</v>
+        <v>3.6711</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2734,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>50.1</v>
+        <v>50.78</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2753,15 +2818,15 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>77.36</v>
+        <v>93.62</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -2772,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6774</v>
+        <v>0.7477</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2783,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -2791,10 +2856,10 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1.685</v>
+        <v>1.581</v>
       </c>
       <c r="W10" t="n">
-        <v>79.3</v>
+        <v>79.7</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -2813,7 +2878,7 @@
         <v>25.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -2833,11 +2898,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.0091</v>
+        <v>3.0108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2849,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>47.31</v>
+        <v>47.59</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2868,15 +2933,15 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>54.18</v>
+        <v>71.86</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -2887,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5853</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2898,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2906,7 +2971,7 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="W11" t="n">
         <v>11.1</v>
@@ -2925,10 +2990,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>53.1</v>
+        <v>51.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -2939,20 +3004,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.3906</v>
+        <v>2.4267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2964,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>51.85</v>
+        <v>61.93</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2983,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>115.28</v>
+        <v>114.69</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3002,18 +3067,18 @@
         <v>-1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7489</v>
+        <v>1.0131</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>14.1</v>
+        <v>15.5</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3021,29 +3086,29 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.725</v>
+        <v>0.893</v>
       </c>
       <c r="W12" t="n">
-        <v>92.8</v>
+        <v>80.5</v>
       </c>
       <c r="X12" t="n">
         <v>-1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>24.8</v>
+        <v>37.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -3054,20 +3119,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>012832</t>
+          <t>110020</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>南方中证新能源ETF联接C</t>
+          <t>易方达沪深300ETF联接A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7282999999999999</v>
+        <v>1.9046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3079,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>54.11</v>
+        <v>61.99</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3098,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>111.32</v>
+        <v>114.73</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3117,18 +3182,18 @@
         <v>-1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6775</v>
+        <v>1.0132</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>12.8</v>
+        <v>15.6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3136,13 +3201,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>1.605</v>
+        <v>0.898</v>
       </c>
       <c r="W13" t="n">
-        <v>47.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -3155,10 +3220,10 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>65.01000000000001</v>
+        <v>35.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3169,20 +3234,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>012805</t>
+          <t>515580</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>科技100ETF华泰柏瑞</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7941</v>
+        <v>2.6212</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3194,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>49.52</v>
+        <v>57.21</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3213,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>100.12</v>
+        <v>116.96</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3232,18 +3297,18 @@
         <v>-1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6754</v>
+        <v>0.9544</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T14" t="n">
-        <v>20.4</v>
+        <v>15.2</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3251,13 +3316,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="W14" t="n">
-        <v>48.1</v>
+        <v>90.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -3266,14 +3331,14 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>53.89</v>
+        <v>38.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3284,16 +3349,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.4391</v>
+        <v>1.6486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3309,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>52.11</v>
+        <v>51.82</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3328,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>111.04</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3340,14 +3405,14 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.749</v>
+        <v>0.2414</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -3358,25 +3423,25 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>14.8</v>
+        <v>29.6</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.389</v>
+        <v>2.687</v>
       </c>
       <c r="W15" t="n">
-        <v>93.7</v>
+        <v>89.8</v>
       </c>
       <c r="X15" t="n">
         <v>-1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -3385,10 +3450,10 @@
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>12.06</v>
+        <v>31.68</v>
       </c>
       <c r="AB15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3399,20 +3464,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.401</v>
+        <v>7.4087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3424,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>58.38</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3443,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>114.77</v>
+        <v>106.16</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3462,7 +3527,7 @@
         <v>-1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9116</v>
+        <v>0.9823</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -3473,7 +3538,7 @@
         <v>-1.5</v>
       </c>
       <c r="T16" t="n">
-        <v>14.8</v>
+        <v>21.5</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -3481,13 +3546,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.894</v>
+        <v>0.97</v>
       </c>
       <c r="W16" t="n">
-        <v>78.09999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -3500,7 +3565,7 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>38.83</v>
+        <v>31.24</v>
       </c>
       <c r="AB16" t="n">
         <v>-2.5</v>
@@ -3514,20 +3579,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.3163</v>
+        <v>1.5483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3539,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>66.23</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3558,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>112.3</v>
+        <v>111.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3577,7 +3642,7 @@
         <v>-1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.0512</v>
+        <v>1.004</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3588,7 +3653,7 @@
         <v>-1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3596,10 +3661,10 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>1.025</v>
+        <v>0.092</v>
       </c>
       <c r="W17" t="n">
-        <v>93.7</v>
+        <v>99.8</v>
       </c>
       <c r="X17" t="n">
         <v>-1</v>
@@ -3615,7 +3680,7 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>31.24</v>
+        <v>3.91</v>
       </c>
       <c r="AB17" t="n">
         <v>-2.5</v>
@@ -3629,20 +3694,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>012805</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.7093</v>
+        <v>0.8224</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3654,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>57.04</v>
+        <v>57.64</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3673,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>19.89</v>
+        <v>112.78</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3685,57 +3750,172 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5132</v>
+        <v>1.0952</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>33.7</v>
+        <v>20.1</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>2.73</v>
+        <v>1.528</v>
       </c>
       <c r="W18" t="n">
-        <v>94</v>
+        <v>52.8</v>
       </c>
       <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>011555</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>海富通欣利混合C</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.4455</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>114.64</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
         <v>-1</v>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Q19" t="n">
+        <v>0.9516</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="W19" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="AA18" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AA19" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>持有</t>
         </is>

--- a/fund.xlsx
+++ b/fund.xlsx
@@ -586,52 +586,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.44</v>
+        <v>-1.42</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.53</v>
+        <v>-2.61</v>
       </c>
       <c r="F3" t="n">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.75</v>
+        <v>-1.79</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.440000000000001</v>
+        <v>-5.859999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6500000000000004</v>
+        <v>-1.050000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>17.59</v>
+        <v>17.6</v>
       </c>
       <c r="K3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-0.73</v>
+        <v>18.36</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>-2.51</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4199999999999999</v>
+        <v>-2.09</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.07999999999999999</v>
+        <v>2.87</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>-11.02</v>
+        <v>-15</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>-13.87</v>
+        <v>-12.07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.220000000000001</v>
+        <v>1.51</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>21.57</v>
+        <v>21.11</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.62</v>
+        <v>-2.829999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -651,52 +651,52 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.7899999999999998</v>
+        <v>-2.03</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-3.12</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6.220000000000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-5.29</v>
+        <v>7.32</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-7.37</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-17.31</v>
+        <v>-15.51</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.23</v>
+        <v>-4.32</v>
       </c>
       <c r="J4" t="n">
-        <v>19.13</v>
+        <v>19.6</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39.11</v>
+        <v>40.26</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>-1.64</v>
+        <v>-3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4.45</v>
+        <v>-2.6</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>8.040000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-15.56</v>
+        <v>-20.58</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-24.73999999999999</v>
+        <v>-21.72</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.359999999999999</v>
+        <v>-1.76</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>23.11</v>
       </c>
       <c r="T4" t="n">
-        <v>16.29</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="5">
@@ -716,52 +716,52 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.63</v>
+        <v>-2.32</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-5.680000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.45</v>
+        <v>2.88</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-10.7</v>
+        <v>-12.76</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-22.76</v>
+        <v>-21.74</v>
       </c>
       <c r="I5" t="n">
-        <v>-11.07</v>
+        <v>-9.56</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.27</v>
+        <v>-4.68</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.06</v>
+        <v>-4.470000000000001</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-1.82</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.3199999999999998</v>
+        <v>-3.41</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-5.16</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.32</v>
+        <v>3.6</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-20.97</v>
+        <v>-25.97</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-30.19</v>
+        <v>-27.95</v>
       </c>
       <c r="R5" t="n">
-        <v>-9.199999999999999</v>
+        <v>-7</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2899999999999991</v>
+        <v>-1.17</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-27.88</v>
+        <v>-25.66</v>
       </c>
     </row>
     <row r="6">
@@ -781,52 +781,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9099999999999999</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-3.569999999999999</v>
+        <v>-0.2699999999999998</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.92</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.38</v>
+        <v>-3.95</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>9.84</v>
+        <v>12.94</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>29.44</v>
+        <v>27.94</v>
       </c>
       <c r="I6" t="n">
-        <v>1.459999999999999</v>
+        <v>0.4199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.949999999999999</v>
+        <v>-5.859999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>23.03</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>1.62</v>
+        <v>21.59</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1.36</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.62</v>
+        <v>-0.4</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.15</v>
+        <v>-3.23</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4299999999999997</v>
+        <v>-0.2699999999999996</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>22.01000000000001</v>
+        <v>21.73</v>
       </c>
       <c r="R6" t="n">
-        <v>3.33</v>
+        <v>2.98</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.969999999999999</v>
+        <v>-2.35</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2099999999999991</v>
+        <v>0.4000000000000004</v>
       </c>
     </row>
     <row r="7">
@@ -846,51 +846,51 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2.470000000000001</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>7.82</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.17</v>
+        <v>2.29</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4.359999999999999</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>8.140000000000001</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>29.92</v>
+        <v>28.05</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-20.9</v>
+        <v>-20.87</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-22.52</v>
+        <v>-22.84</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n">
-        <v>3.180000000000001</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-4.15</v>
+      <c r="M7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1.33</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>6.05</v>
+        <v>5.08</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.1</v>
+        <v>-5.069999999999999</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>22.49</v>
+        <v>21.84</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-19.03</v>
+        <v>-18.31</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>-18.54</v>
+        <v>-19.33</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -918,49 +918,49 @@
         <v>-0.09999999999999987</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07000000000000006</v>
+        <v>0.08999999999999986</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1800000000000002</v>
+        <v>-0.2800000000000002</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.41</v>
+        <v>-1.229999999999997</v>
       </c>
       <c r="I8" t="n">
         <v>-0.8000000000000007</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5299999999999994</v>
+        <v>0.5700000000000003</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.8200000000000003</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6100000000000001</v>
+        <v>-1.19</v>
       </c>
       <c r="N8" t="n">
-        <v>2.05</v>
+        <v>0.53</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>-10.45</v>
+        <v>-13.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>-8.839999999999996</v>
+        <v>-7.439999999999998</v>
       </c>
       <c r="R8" t="n">
-        <v>1.07</v>
+        <v>1.76</v>
       </c>
       <c r="S8" t="n">
-        <v>4.51</v>
+        <v>4.08</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>-21.99</v>
+        <v>-20.37</v>
       </c>
     </row>
     <row r="9">
@@ -980,52 +980,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.77</v>
+        <v>0.9300000000000002</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.75</v>
+        <v>-0.47</v>
       </c>
       <c r="F9" t="n">
-        <v>1.72</v>
+        <v>-0.6400000000000001</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>9.469999999999999</v>
+        <v>12.14</v>
       </c>
       <c r="H9" t="n">
-        <v>5.48</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.860000000000001</v>
+        <v>-3.48</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.67</v>
+        <v>-3.19</v>
       </c>
       <c r="K9" t="n">
-        <v>22.54</v>
+        <v>20.97</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.06000000000000005</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2000000000000002</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.04999999999999999</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8000000000000007</v>
+        <v>-1.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.949999999999996</v>
+        <v>-1.710000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.9900000000000002</v>
+        <v>-0.9199999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3100000000000005</v>
+        <v>0.3200000000000003</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2799999999999994</v>
+        <v>-0.2199999999999989</v>
       </c>
     </row>
     <row r="10">
@@ -1045,52 +1045,52 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.38</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4.84</v>
       </c>
       <c r="F10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6.789999999999999</v>
+        <v>-0.2800000000000002</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>8.720000000000001</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>32.15000000000001</v>
+        <v>29.85</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04999999999999893</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>-15.39</v>
+        <v>-1.830000000000001</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-13.29</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6699999999999999</v>
+        <v>0.6300000000000008</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.51</v>
+        <v>3.29</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>5.36</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.21</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.48</v>
+        <v>-4.489999999999998</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>24.72000000000001</v>
+        <v>23.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.92</v>
+        <v>0.7299999999999995</v>
       </c>
       <c r="S10" t="n">
-        <v>-11.41</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>-22.15</v>
+        <v>-20.56</v>
       </c>
     </row>
     <row r="11">
@@ -1110,52 +1110,52 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4.390000000000001</v>
+        <v>2.88</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5700000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.19</v>
+        <v>-2.91</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.79</v>
+        <v>-3.53</v>
       </c>
       <c r="H11" t="n">
-        <v>2.439999999999998</v>
+        <v>8.990000000000002</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.840000000000001</v>
+        <v>-7.800000000000001</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>51.64</v>
+        <v>50.28</v>
       </c>
       <c r="K11" t="n">
-        <v>10.05</v>
+        <v>8.379999999999999</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5.100000000000001</v>
+        <v>1.79</v>
       </c>
       <c r="N11" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>-5.96</v>
+        <v>1.64</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-2.19</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-12.06</v>
+        <v>-16.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.989999999999998</v>
+        <v>2.780000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>-4.97</v>
+        <v>-5.24</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>55.62</v>
+        <v>53.79</v>
       </c>
       <c r="T11" t="n">
-        <v>-12.77</v>
+        <v>-12.81</v>
       </c>
     </row>
     <row r="12">
@@ -1174,53 +1174,53 @@
           <t>619.61</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>2.69</v>
+      <c r="D12" t="n">
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.85</v>
+        <v>-2.65</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7200000000000002</v>
+        <v>-2.01</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.960000000000001</v>
+        <v>0.3200000000000003</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.630000000000001</v>
+        <v>-3.550000000000001</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>36.43</v>
+        <v>35.65000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>-5.62</v>
+        <v>15.54</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.0900000000000003</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1.93</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>-10.99</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>-12.39</v>
+        <v>-15.22</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-5.890000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.7599999999999998</v>
+        <v>-0.9900000000000002</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>40.41</v>
+        <v>39.16</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.95</v>
+        <v>-5.649999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1239,52 +1239,52 @@
           <t>655.24</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>-2.33</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.09000000000000008</v>
+      <c r="D13" s="2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-5</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-14.1</v>
+        <v>-11.62</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-9.290000000000001</v>
+        <v>-6.15</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.129999999999999</v>
+        <v>-8.089999999999998</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35.32</v>
+        <v>36.68</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.9</v>
+        <v>-7.039999999999999</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="M13" s="3" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2.04</v>
+      <c r="M13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>-4.48</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-15.87</v>
+        <v>-10.9</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>-19.56</v>
+        <v>-19.36</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-14.56</v>
+        <v>-14.3</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>37.19</v>
+        <v>39.23999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.08000000000000007</v>
+        <v>-3.529999999999999</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1308,53 +1308,53 @@
           <t>1947.62</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>-2.38</v>
+      <c r="D14" t="n">
+        <v>-1.48</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-4.75</v>
+        <v>-6.11</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>10.84</v>
+        <v>9.82</v>
       </c>
       <c r="G14" t="n">
-        <v>4.19</v>
+        <v>-1.63</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2399999999999984</v>
+        <v>4.020000000000003</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>24.91</v>
+        <v>27.89</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>34.11</v>
+        <v>37.17</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>32.62</v>
+        <v>30.97</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-2.8</v>
+        <v>-2.57</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>-5.59</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>9.069999999999999</v>
+        <v>10.54</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>-6.08</v>
+        <v>-14.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.189999999999998</v>
+        <v>-2.189999999999998</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>26.78</v>
+        <v>30.45</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>38.09</v>
+        <v>40.68</v>
       </c>
       <c r="T14" t="n">
-        <v>9.799999999999999</v>
+        <v>9.780000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1373,53 +1373,53 @@
           <t>271.58</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>-9.98</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>8.57</v>
+      <c r="D15" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.74</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>50.94</v>
+        <v>54.03</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3999999999999999</v>
+        <v>-3.55</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-25.06</v>
+        <v>-23.17</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>-27.62</v>
+        <v>-27.03</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>24.49</v>
+        <v>25.06</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>70.22</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>-9.27</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>10.52</v>
+        <v>-2.38</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.22</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>49.17</v>
+        <v>54.75</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-10.67</v>
+        <v>-16.76</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>-32.48999999999999</v>
+        <v>-29.38</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-25.75</v>
+        <v>-24.47</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>28.47</v>
+        <v>28.57</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>47.4</v>
+        <v>49.32</v>
       </c>
     </row>
     <row r="19">
@@ -1569,25 +1569,25 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.06</v>
+        <v>0.08999999999999997</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-2.06</v>
+        <v>-1.42</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1.27</v>
+        <v>0.8899999999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2.88</v>
+        <v>4.02</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>15.06</v>
+        <v>13.79</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8.739999999999998</v>
+        <v>8.43</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-7.22</v>
+        <v>-7.77</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-1.51</v>
+        <v>-0.96</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>1.29</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>2.43</v>
+        <v>3.37</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>12.03</v>
+        <v>11.1</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>11.8</v>
+        <v>11.45</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -1661,29 +1661,29 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="2" t="n">
-        <v>0.04000000000000001</v>
+      <c r="M22" t="n">
+        <v>0.02000000000000002</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="O22" t="n">
-        <v>0.02000000000000002</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.65</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>-3.03</v>
+        <v>-2.69</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>7.52</v>
+        <v>7.73</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
     </row>
   </sheetData>
@@ -1854,20 +1854,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>012832</t>
+          <t>110026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>南方中证新能源ETF联接C</t>
+          <t>易方达创业板ETF联接A</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7462</v>
+        <v>3.7326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>59</v>
+        <v>69.62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>118.33</v>
+        <v>113.35</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>-1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8681</v>
+        <v>1.0477</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>-1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>13.2</v>
+        <v>17.1</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1936,13 +1936,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>1.613</v>
+        <v>1.563</v>
       </c>
       <c r="W2" t="n">
-        <v>50.2</v>
+        <v>100</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>65.01000000000001</v>
+        <v>54.99</v>
       </c>
       <c r="AB2" t="n">
         <v>-2.5</v>
@@ -1969,20 +1969,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>050025</t>
+          <t>510310</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>博时标普500ETF联接A</t>
+          <t>沪深300ETF易方达</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.2477</v>
+        <v>2.4229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>67.7</v>
+        <v>61.11</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>105.56</v>
+        <v>110.77</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>-1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9643</v>
+        <v>0.9345</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>-1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>22.8</v>
+        <v>16</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.71</v>
+        <v>0.842</v>
       </c>
       <c r="W3" t="n">
-        <v>98</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>-1</v>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>18.73</v>
+        <v>37.6</v>
       </c>
       <c r="AB3" t="n">
         <v>-2.5</v>
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.9222</v>
+        <v>1.9297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>58.58</v>
+        <v>59.54</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>111.92</v>
+        <v>110.76</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>-1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9996</v>
+        <v>0.9711</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>-1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>1.264</v>
+        <v>1.197</v>
       </c>
       <c r="W4" t="n">
-        <v>89.8</v>
+        <v>90.5</v>
       </c>
       <c r="X4" t="n">
         <v>-1</v>
@@ -2199,20 +2199,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>161119</t>
+          <t>050025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>易方达中债新综指发起式(LOF)A</t>
+          <t>博时标普500ETF联接A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.7737</v>
+        <v>5.267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2224,67 +2224,67 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>82.70999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="P5" t="n">
         <v>-1</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>98.12</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>持有</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.904</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
       <c r="S5" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>50.6</v>
+        <v>24</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.037</v>
+        <v>0.68</v>
       </c>
       <c r="W5" t="n">
-        <v>99.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="X5" t="n">
         <v>-1</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>1.88</v>
+        <v>18.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3</v>
+        <v>-2.5</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2314,20 +2314,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>110026</t>
+          <t>519769</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>易方达创业板ETF联接A</t>
+          <t>交银优选回报灵活配置混合C</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.6826</v>
+        <v>1.5483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>67.64</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>114.69</v>
+        <v>109.64</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>-1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.0708</v>
+        <v>0.9414</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>-1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>15.4</v>
+        <v>17.7</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.602</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="X6" t="n">
         <v>-1</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>54.99</v>
+        <v>3.91</v>
       </c>
       <c r="AB6" t="n">
         <v>-2.5</v>
@@ -2429,20 +2429,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>501060</t>
+          <t>510580</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中金中证优选300指数(LOF)A</t>
+          <t>中证500ETF易方达</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.3998</v>
+        <v>1.6212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>53.75</v>
+        <v>59.49</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>115.84</v>
+        <v>110.75</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>-1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8985</v>
+        <v>0.9724</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>-1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>13.6</v>
+        <v>16</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2511,26 +2511,26 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.698</v>
+        <v>1.259</v>
       </c>
       <c r="W7" t="n">
-        <v>93.5</v>
+        <v>90.5</v>
       </c>
       <c r="X7" t="n">
         <v>-1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>24.8</v>
+        <v>38.31</v>
       </c>
       <c r="AB7" t="n">
         <v>-2.5</v>
@@ -2544,20 +2544,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>008115</t>
+          <t>040046</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>天弘中证红利低波动100联接C</t>
+          <t>华安纳斯达克100ETF联接(QDII)A</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.7653</v>
+        <v>7.5222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2569,15 +2569,15 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>47.05</v>
+        <v>72.44</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>60.18</v>
+        <v>105.34</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2600,25 +2600,25 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4129</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>11.7</v>
+        <v>23.4</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -2626,53 +2626,53 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.486</v>
+        <v>0.978</v>
       </c>
       <c r="W8" t="n">
-        <v>93.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="X8" t="n">
         <v>-1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>13.26</v>
+        <v>31.24</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>持有</t>
+        <v>-4</v>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>卖出</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>510580</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中证500ETF易方达</t>
+          <t>消费ETF汇添富</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.6144</v>
+        <v>2.9664</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>58.5</v>
+        <v>41.43</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2703,67 +2703,67 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>111.89</v>
+        <v>24.84</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2545</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="W9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="AB9" t="n">
         <v>-1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>震荡</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>1.329</v>
-      </c>
-      <c r="W9" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="AA9" t="n">
-        <v>38.31</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-2.5</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>000216</t>
+          <t>006476</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>华安黄金ETF联接A</t>
+          <t>南方原油C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.6711</v>
+        <v>1.6762</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>50.78</v>
+        <v>54.02</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>93.62</v>
+        <v>12.04</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7477</v>
+        <v>0.3813</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2848,25 +2848,25 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>11.8</v>
+        <v>28.1</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>1.581</v>
+        <v>2.571</v>
       </c>
       <c r="W10" t="n">
-        <v>79.7</v>
+        <v>91.7</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>25.07</v>
+        <v>31.68</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -2889,20 +2889,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>000216</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>消费ETF汇添富</t>
+          <t>华安黄金ETF联接A</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.0108</v>
+        <v>3.6524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>47.59</v>
+        <v>49.56</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>71.86</v>
+        <v>87.23</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5853</v>
+        <v>0.7123</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>13.6</v>
+        <v>11</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.763</v>
+        <v>1.513</v>
       </c>
       <c r="W11" t="n">
-        <v>11.1</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2986,11 +2986,11 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>51.33</v>
+        <v>25.07</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -3004,20 +3004,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>012805</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>沪深300ETF易方达</t>
+          <t>广发恒生科技ETF联接(QDII)C</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.4267</v>
+        <v>0.8154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>61.93</v>
+        <v>55.27</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>114.69</v>
+        <v>108.59</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>-1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.0131</v>
+        <v>0.9769</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>-1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>15.5</v>
+        <v>19.4</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3086,26 +3086,26 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.893</v>
+        <v>1.493</v>
       </c>
       <c r="W12" t="n">
-        <v>80.5</v>
+        <v>51.6</v>
       </c>
       <c r="X12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>37.6</v>
+        <v>53.89</v>
       </c>
       <c r="AB12" t="n">
         <v>-2.5</v>
@@ -3119,20 +3119,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>110020</t>
+          <t>501060</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>易方达沪深300ETF联接A</t>
+          <t>中金中证优选300指数(LOF)A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.9046</v>
+        <v>2.3873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>61.99</v>
+        <v>50.83</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>114.73</v>
+        <v>101.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3182,18 +3182,18 @@
         <v>-1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.0132</v>
+        <v>0.7945</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>15.6</v>
+        <v>12.8</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3201,29 +3201,29 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.898</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>82.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="X13" t="n">
         <v>-1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>35.9</v>
+        <v>24.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3243,11 +3243,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.6212</v>
+        <v>2.612</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>57.21</v>
+        <v>56.02</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>116.96</v>
+        <v>110.94</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>-1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.9544</v>
+        <v>0.8858</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>-1.5</v>
       </c>
       <c r="T14" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>1.27</v>
+        <v>1.209</v>
       </c>
       <c r="W14" t="n">
-        <v>90.5</v>
+        <v>90</v>
       </c>
       <c r="X14" t="n">
         <v>-1</v>
@@ -3349,20 +3349,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>006476</t>
+          <t>012832</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>南方原油C</t>
+          <t>南方中证新能源ETF联接C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.6486</v>
+        <v>0.7467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3374,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>51.82</v>
+        <v>59.13</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>119.06</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3405,39 +3405,39 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2414</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="T15" t="n">
-        <v>29.6</v>
+        <v>13.5</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>2.687</v>
+        <v>1.501</v>
       </c>
       <c r="W15" t="n">
-        <v>89.8</v>
+        <v>50.3</v>
       </c>
       <c r="X15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>31.68</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3464,20 +3464,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>040046</t>
+          <t>008115</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>华安纳斯达克100ETF联接(QDII)A</t>
+          <t>天弘中证红利低波动100联接C</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.4087</v>
+        <v>1.7567</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>68.84999999999999</v>
+        <v>43.68</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>106.16</v>
+        <v>46.62</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3520,25 +3520,25 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9823</v>
+        <v>0.2931</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>卖出</t>
+          <t>持有</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>21.5</v>
+        <v>11.8</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -3546,29 +3546,29 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.97</v>
+        <v>0.488</v>
       </c>
       <c r="W16" t="n">
-        <v>95.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="X16" t="n">
         <v>-1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>31.24</v>
+        <v>13.26</v>
       </c>
       <c r="AB16" t="n">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -3579,20 +3579,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>519769</t>
+          <t>011555</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>交银优选回报灵活配置混合C</t>
+          <t>海富通欣利混合C</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.5483</v>
+        <v>1.443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3604,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>64.18000000000001</v>
+        <v>54.21</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>111.8</v>
+        <v>105.23</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>-1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.004</v>
+        <v>0.8645</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>-1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>16.9</v>
+        <v>14.3</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -3661,26 +3661,26 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.092</v>
+        <v>0.364</v>
       </c>
       <c r="W17" t="n">
-        <v>99.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="X17" t="n">
         <v>-1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
       <c r="AA17" t="n">
-        <v>3.91</v>
+        <v>12.06</v>
       </c>
       <c r="AB17" t="n">
         <v>-2.5</v>
@@ -3694,20 +3694,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>012805</t>
+          <t>110020</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>广发恒生科技ETF联接(QDII)C</t>
+          <t>易方达沪深300ETF联接A</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.8224</v>
+        <v>1.9016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>57.64</v>
+        <v>61.16</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>112.78</v>
+        <v>110.79</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>-1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.0952</v>
+        <v>0.9347</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>-1.5</v>
       </c>
       <c r="T18" t="n">
-        <v>20.1</v>
+        <v>16.1</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -3776,26 +3776,26 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>1.528</v>
+        <v>0.846</v>
       </c>
       <c r="W18" t="n">
-        <v>52.8</v>
+        <v>82</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>53.89</v>
+        <v>35.9</v>
       </c>
       <c r="AB18" t="n">
         <v>-2.5</v>
@@ -3809,20 +3809,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>011555</t>
+          <t>161119</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>海富通欣利混合C</t>
+          <t>易方达中债新综指发起式(LOF)A</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.4455</v>
+        <v>1.7761</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3834,15 +3834,15 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>56.12</v>
+        <v>86.47</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>卖出</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -3853,55 +3853,55 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>114.64</v>
+        <v>99.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>持有</t>
+          <t>买入</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>持有</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.0065</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>卖出</t>
         </is>
       </c>
-      <c r="P19" t="n">
+      <c r="S19" t="n">
         <v>-1</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0.9516</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>卖出</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.5</v>
-      </c>
       <c r="T19" t="n">
-        <v>14.8</v>
+        <v>52.2</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.379</v>
+        <v>0.044</v>
       </c>
       <c r="W19" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="X19" t="n">
         <v>-1</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>12.06</v>
+        <v>1.88</v>
       </c>
       <c r="AB19" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
